--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/64.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/64.xlsx
@@ -426,13 +426,13 @@
         <v>-9.378091347272408</v>
       </c>
       <c r="E2">
-        <v>-10.63902229984204</v>
+        <v>-8.085773556363332</v>
       </c>
       <c r="F2">
-        <v>0.3112464788433645</v>
+        <v>-0.6413694074368446</v>
       </c>
       <c r="G2">
-        <v>-8.022641387025757</v>
+        <v>-7.727347852783529</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.417757757877894</v>
       </c>
       <c r="E3">
-        <v>-10.30369785652207</v>
+        <v>-8.607847739285624</v>
       </c>
       <c r="F3">
-        <v>0.2946401975194428</v>
+        <v>-0.075326908653678</v>
       </c>
       <c r="G3">
-        <v>-8.317147428093717</v>
+        <v>-8.067567872617673</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.381388745276588</v>
       </c>
       <c r="E4">
-        <v>-10.86262928939279</v>
+        <v>-9.052349162456524</v>
       </c>
       <c r="F4">
-        <v>0.1985106455267686</v>
+        <v>0.06279672882391717</v>
       </c>
       <c r="G4">
-        <v>-8.234792048173214</v>
+        <v>-7.099138297898482</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.265380368016423</v>
       </c>
       <c r="E5">
-        <v>-10.76624524861353</v>
+        <v>-9.671821764335791</v>
       </c>
       <c r="F5">
-        <v>0.40126019430117</v>
+        <v>-0.03483051143301857</v>
       </c>
       <c r="G5">
-        <v>-7.803501723956682</v>
+        <v>-7.557390419668971</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.071559554003979</v>
       </c>
       <c r="E6">
-        <v>-11.94880642250256</v>
+        <v>-9.412421716228417</v>
       </c>
       <c r="F6">
-        <v>-0.0020984018787989</v>
+        <v>0.3771803822691912</v>
       </c>
       <c r="G6">
-        <v>-7.272964291231625</v>
+        <v>-8.062852757236751</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.803445299105558</v>
       </c>
       <c r="E7">
-        <v>-12.50926395111387</v>
+        <v>-10.84376366667683</v>
       </c>
       <c r="F7">
-        <v>0.6655665531450055</v>
+        <v>0.08464657580755973</v>
       </c>
       <c r="G7">
-        <v>-7.523908834876398</v>
+        <v>-8.469566731973043</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.467664829384882</v>
       </c>
       <c r="E8">
-        <v>-12.22545995657916</v>
+        <v>-11.58911426054731</v>
       </c>
       <c r="F8">
-        <v>0.1185466833997267</v>
+        <v>0.6758962946579152</v>
       </c>
       <c r="G8">
-        <v>-7.15717654484194</v>
+        <v>-7.786842962099381</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.085367714618229</v>
       </c>
       <c r="E9">
-        <v>-12.78479442363656</v>
+        <v>-10.89700946405902</v>
       </c>
       <c r="F9">
-        <v>0.9806534905152562</v>
+        <v>0.3339760520087801</v>
       </c>
       <c r="G9">
-        <v>-6.907511677605351</v>
+        <v>-6.864717986027073</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.676238986133895</v>
       </c>
       <c r="E10">
-        <v>-13.57631733848925</v>
+        <v>-13.12716064403847</v>
       </c>
       <c r="F10">
-        <v>0.6337497895708792</v>
+        <v>0.8964565709599088</v>
       </c>
       <c r="G10">
-        <v>-6.737619868921982</v>
+        <v>-5.851713016422825</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.260770780934984</v>
       </c>
       <c r="E11">
-        <v>-15.61257737535628</v>
+        <v>-13.41914306263103</v>
       </c>
       <c r="F11">
-        <v>0.7835500939583362</v>
+        <v>0.497729376928992</v>
       </c>
       <c r="G11">
-        <v>-7.065709212650859</v>
+        <v>-7.395439167159458</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.857067445442112</v>
       </c>
       <c r="E12">
-        <v>-16.27475348712788</v>
+        <v>-13.72245119471677</v>
       </c>
       <c r="F12">
-        <v>0.6635461650495774</v>
+        <v>1.320685055486008</v>
       </c>
       <c r="G12">
-        <v>-5.021544274553955</v>
+        <v>-5.844199019051697</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.482030105100264</v>
       </c>
       <c r="E13">
-        <v>-17.28913166484604</v>
+        <v>-14.3597297563942</v>
       </c>
       <c r="F13">
-        <v>0.7229384510954964</v>
+        <v>0.7415021645922333</v>
       </c>
       <c r="G13">
-        <v>-4.703403594593314</v>
+        <v>-3.881493687389567</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.160958736820007</v>
       </c>
       <c r="E14">
-        <v>-17.30163931005522</v>
+        <v>-14.24278644362012</v>
       </c>
       <c r="F14">
-        <v>0.9060623193627719</v>
+        <v>1.309909652310392</v>
       </c>
       <c r="G14">
-        <v>-4.284562224973315</v>
+        <v>-4.889458700678508</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.908423998549739</v>
       </c>
       <c r="E15">
-        <v>-17.55334095234956</v>
+        <v>-16.95189620549483</v>
       </c>
       <c r="F15">
-        <v>1.030401923257783</v>
+        <v>1.458051565157445</v>
       </c>
       <c r="G15">
-        <v>-4.40147543035789</v>
+        <v>-3.742711140311293</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.734243111142538</v>
       </c>
       <c r="E16">
-        <v>-19.29932127685091</v>
+        <v>-16.7673835320523</v>
       </c>
       <c r="F16">
-        <v>1.206070484899863</v>
+        <v>1.794983379306921</v>
       </c>
       <c r="G16">
-        <v>-3.458376886077611</v>
+        <v>-3.050691669759724</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.637515507454861</v>
       </c>
       <c r="E17">
-        <v>-19.63149843073555</v>
+        <v>-18.6008313320118</v>
       </c>
       <c r="F17">
-        <v>0.9567501207400736</v>
+        <v>2.182863102198179</v>
       </c>
       <c r="G17">
-        <v>-2.933381436566457</v>
+        <v>-4.25357436856592</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.619932944666574</v>
       </c>
       <c r="E18">
-        <v>-19.96726666450828</v>
+        <v>-19.23966316027386</v>
       </c>
       <c r="F18">
-        <v>1.494678658239628</v>
+        <v>1.383950787507418</v>
       </c>
       <c r="G18">
-        <v>-2.677816932965986</v>
+        <v>-2.154504750114827</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.683215087215714</v>
       </c>
       <c r="E19">
-        <v>-21.38565265082075</v>
+        <v>-20.36563652296304</v>
       </c>
       <c r="F19">
-        <v>1.715778201720844</v>
+        <v>1.40706389478033</v>
       </c>
       <c r="G19">
-        <v>-1.743781122632894</v>
+        <v>-2.364896676506422</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.820620026228045</v>
       </c>
       <c r="E20">
-        <v>-22.45751527759228</v>
+        <v>-20.66705175291358</v>
       </c>
       <c r="F20">
-        <v>1.487766760630669</v>
+        <v>2.228506146092431</v>
       </c>
       <c r="G20">
-        <v>-2.129239344107102</v>
+        <v>-2.577057181318558</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.02196634371167</v>
       </c>
       <c r="E21">
-        <v>-23.17850268130149</v>
+        <v>-21.36691835385102</v>
       </c>
       <c r="F21">
-        <v>1.553383399341223</v>
+        <v>1.809768080712087</v>
       </c>
       <c r="G21">
-        <v>-1.190284982656403</v>
+        <v>-1.214270712255944</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.269887168903521</v>
       </c>
       <c r="E22">
-        <v>-23.65890131793119</v>
+        <v>-21.60914642852131</v>
       </c>
       <c r="F22">
-        <v>2.061909864245812</v>
+        <v>2.232929628023381</v>
       </c>
       <c r="G22">
-        <v>-0.8791562731682954</v>
+        <v>-1.014368851189893</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.556809071926449</v>
       </c>
       <c r="E23">
-        <v>-23.5346898043748</v>
+        <v>-23.85005273426897</v>
       </c>
       <c r="F23">
-        <v>1.500048135744574</v>
+        <v>2.69863115493804</v>
       </c>
       <c r="G23">
-        <v>-0.8217841142014045</v>
+        <v>-2.985382235840537</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.874001871322553</v>
       </c>
       <c r="E24">
-        <v>-24.89829484061649</v>
+        <v>-23.11558859191292</v>
       </c>
       <c r="F24">
-        <v>1.686609728733468</v>
+        <v>1.757859265783059</v>
       </c>
       <c r="G24">
-        <v>-0.49870191457224</v>
+        <v>-0.147696519472201</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.209659590339843</v>
       </c>
       <c r="E25">
-        <v>-25.29077315438727</v>
+        <v>-22.89226689622466</v>
       </c>
       <c r="F25">
-        <v>1.811202813053736</v>
+        <v>1.967916671784957</v>
       </c>
       <c r="G25">
-        <v>-0.5360323722540425</v>
+        <v>-1.048398399982894</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.550228598145558</v>
       </c>
       <c r="E26">
-        <v>-24.6356976898597</v>
+        <v>-24.21808634534634</v>
       </c>
       <c r="F26">
-        <v>2.259122605299901</v>
+        <v>2.111613565148588</v>
       </c>
       <c r="G26">
-        <v>-0.4058827190986679</v>
+        <v>-1.11561094240656</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.880023546123286</v>
       </c>
       <c r="E27">
-        <v>-25.35029994521809</v>
+        <v>-23.05475760056789</v>
       </c>
       <c r="F27">
-        <v>1.576619104989749</v>
+        <v>2.574240192264055</v>
       </c>
       <c r="G27">
-        <v>0.4938019827285976</v>
+        <v>0.5767545449729194</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.19483209496723</v>
       </c>
       <c r="E28">
-        <v>-25.17514762754942</v>
+        <v>-23.96675603792064</v>
       </c>
       <c r="F28">
-        <v>2.312751110957141</v>
+        <v>3.290256124221864</v>
       </c>
       <c r="G28">
-        <v>0.7480343103759336</v>
+        <v>0.7763184402183471</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.488938169544079</v>
       </c>
       <c r="E29">
-        <v>-24.24224122570326</v>
+        <v>-23.19757208534779</v>
       </c>
       <c r="F29">
-        <v>1.985065533757713</v>
+        <v>2.001084502593049</v>
       </c>
       <c r="G29">
-        <v>-0.3528384913686846</v>
+        <v>0.2858053480753971</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.755956639559169</v>
       </c>
       <c r="E30">
-        <v>-23.10449383059413</v>
+        <v>-22.02932541779701</v>
       </c>
       <c r="F30">
-        <v>1.739288925347099</v>
+        <v>2.516799539819132</v>
       </c>
       <c r="G30">
-        <v>0.3314569836319514</v>
+        <v>-0.07438418616952772</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.987495268627551</v>
       </c>
       <c r="E31">
-        <v>-24.03641302510663</v>
+        <v>-22.76565529144421</v>
       </c>
       <c r="F31">
-        <v>2.0538581330906</v>
+        <v>1.875424481057976</v>
       </c>
       <c r="G31">
-        <v>-0.2120543991391496</v>
+        <v>-0.3758300108357138</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.176073038496789</v>
       </c>
       <c r="E32">
-        <v>-23.70648652280379</v>
+        <v>-21.63247259813481</v>
       </c>
       <c r="F32">
-        <v>1.58022913013115</v>
+        <v>2.231577732422012</v>
       </c>
       <c r="G32">
-        <v>-0.5298046137342165</v>
+        <v>0.05354407999010287</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.325162654910525</v>
       </c>
       <c r="E33">
-        <v>-23.96960444807146</v>
+        <v>-23.10822982165046</v>
       </c>
       <c r="F33">
-        <v>1.946022921328966</v>
+        <v>2.355004475439138</v>
       </c>
       <c r="G33">
-        <v>-0.443180364564876</v>
+        <v>-1.091694118459767</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.436603195356632</v>
       </c>
       <c r="E34">
-        <v>-22.34135539082153</v>
+        <v>-20.23935549678514</v>
       </c>
       <c r="F34">
-        <v>2.198964907773795</v>
+        <v>2.644293566784004</v>
       </c>
       <c r="G34">
-        <v>-0.4539788647170085</v>
+        <v>-0.1444120166911968</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.512568877514163</v>
       </c>
       <c r="E35">
-        <v>-22.6170488884085</v>
+        <v>-20.96468117859371</v>
       </c>
       <c r="F35">
-        <v>1.712837497440906</v>
+        <v>2.243953541419837</v>
       </c>
       <c r="G35">
-        <v>-0.5295782094466148</v>
+        <v>0.4797485107894959</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.551985278355065</v>
       </c>
       <c r="E36">
-        <v>-22.25638763301561</v>
+        <v>-20.60362594596215</v>
       </c>
       <c r="F36">
-        <v>1.934135849098793</v>
+        <v>2.549240064047567</v>
       </c>
       <c r="G36">
-        <v>-0.8804654805705138</v>
+        <v>-1.546389396059819</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.556693409510832</v>
       </c>
       <c r="E37">
-        <v>-22.23353242469889</v>
+        <v>-19.71391212920114</v>
       </c>
       <c r="F37">
-        <v>1.865167635876512</v>
+        <v>1.979976044434913</v>
       </c>
       <c r="G37">
-        <v>-2.730877566803767</v>
+        <v>-2.026103988050636</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.538242388366264</v>
       </c>
       <c r="E38">
-        <v>-19.94548923300539</v>
+        <v>-19.1199574783551</v>
       </c>
       <c r="F38">
-        <v>2.560886909730927</v>
+        <v>2.448729276861485</v>
       </c>
       <c r="G38">
-        <v>-1.600696894090188</v>
+        <v>-1.207885455101264</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.501560009405772</v>
       </c>
       <c r="E39">
-        <v>-21.87689245422482</v>
+        <v>-18.28833039769049</v>
       </c>
       <c r="F39">
-        <v>2.617757645402725</v>
+        <v>2.265825754323355</v>
       </c>
       <c r="G39">
-        <v>-1.703336785691179</v>
+        <v>-2.190233971675621</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.449483298353559</v>
       </c>
       <c r="E40">
-        <v>-19.85837950699385</v>
+        <v>-18.24992893810544</v>
       </c>
       <c r="F40">
-        <v>2.378344555380417</v>
+        <v>2.708737237252195</v>
       </c>
       <c r="G40">
-        <v>-2.448430014966766</v>
+        <v>-2.62538301244606</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.378406977660999</v>
       </c>
       <c r="E41">
-        <v>-20.5099001194254</v>
+        <v>-17.15322310292784</v>
       </c>
       <c r="F41">
-        <v>2.381711040505394</v>
+        <v>2.874114162281893</v>
       </c>
       <c r="G41">
-        <v>-2.569388966534136</v>
+        <v>-1.341060394534447</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.291696389124191</v>
       </c>
       <c r="E42">
-        <v>-18.77421301634348</v>
+        <v>-16.59329540577543</v>
       </c>
       <c r="F42">
-        <v>2.501262680812224</v>
+        <v>2.491287480547713</v>
       </c>
       <c r="G42">
-        <v>-1.559527407183835</v>
+        <v>-2.879192062512228</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.19869083117576</v>
       </c>
       <c r="E43">
-        <v>-17.67656978704628</v>
+        <v>-14.64592025673095</v>
       </c>
       <c r="F43">
-        <v>2.448310122955669</v>
+        <v>2.844866166023849</v>
       </c>
       <c r="G43">
-        <v>-2.248567528559429</v>
+        <v>-3.450108207747811</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.10328819568338</v>
       </c>
       <c r="E44">
-        <v>-18.41291777458951</v>
+        <v>-14.82223186374559</v>
       </c>
       <c r="F44">
-        <v>2.766482728901348</v>
+        <v>2.298463429993655</v>
       </c>
       <c r="G44">
-        <v>-2.653470268994906</v>
+        <v>-2.860177383575245</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.008315377647667</v>
       </c>
       <c r="E45">
-        <v>-16.8893579794489</v>
+        <v>-14.34193738201806</v>
       </c>
       <c r="F45">
-        <v>2.597103132581322</v>
+        <v>2.980811197232081</v>
       </c>
       <c r="G45">
-        <v>-3.369239221193736</v>
+        <v>-3.402497682920268</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.910047422723451</v>
       </c>
       <c r="E46">
-        <v>-15.71322723865076</v>
+        <v>-12.48748199113697</v>
       </c>
       <c r="F46">
-        <v>2.908358870713625</v>
+        <v>2.681285141523419</v>
       </c>
       <c r="G46">
-        <v>-3.147723953715623</v>
+        <v>-3.06419061525528</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.81459691408458</v>
       </c>
       <c r="E47">
-        <v>-14.77734110090755</v>
+        <v>-13.52829740011191</v>
       </c>
       <c r="F47">
-        <v>3.009833877556564</v>
+        <v>2.504122205086689</v>
       </c>
       <c r="G47">
-        <v>-3.605090145665063</v>
+        <v>-2.189626945687123</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.728511694008976</v>
       </c>
       <c r="E48">
-        <v>-14.19524199501359</v>
+        <v>-12.64946550639134</v>
       </c>
       <c r="F48">
-        <v>3.024340247514389</v>
+        <v>3.333556545101</v>
       </c>
       <c r="G48">
-        <v>-3.869550040913188</v>
+        <v>-4.507682009793997</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.652994532773736</v>
       </c>
       <c r="E49">
-        <v>-13.91383356322894</v>
+        <v>-9.927730358983251</v>
       </c>
       <c r="F49">
-        <v>2.796956708915536</v>
+        <v>3.234349608206926</v>
       </c>
       <c r="G49">
-        <v>-5.146706470938974</v>
+        <v>-4.666749068552758</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.586181060806815</v>
       </c>
       <c r="E50">
-        <v>-13.37956419980399</v>
+        <v>-9.722110468190969</v>
       </c>
       <c r="F50">
-        <v>2.862439152106837</v>
+        <v>3.868433377088641</v>
       </c>
       <c r="G50">
-        <v>-3.829542106438879</v>
+        <v>-4.892739922237952</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.52099675204148</v>
       </c>
       <c r="E51">
-        <v>-11.93605876817097</v>
+        <v>-9.551002077811145</v>
       </c>
       <c r="F51">
-        <v>2.647191195958997</v>
+        <v>3.546367444349804</v>
       </c>
       <c r="G51">
-        <v>-2.983282254042492</v>
+        <v>-5.091434293770128</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.460217064589786</v>
       </c>
       <c r="E52">
-        <v>-11.70071397399234</v>
+        <v>-8.498756800440846</v>
       </c>
       <c r="F52">
-        <v>3.087047659906312</v>
+        <v>3.0533413902864</v>
       </c>
       <c r="G52">
-        <v>-4.750617091612164</v>
+        <v>-6.069704251946094</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.403877982941514</v>
       </c>
       <c r="E53">
-        <v>-11.48417140389356</v>
+        <v>-7.693204673112397</v>
       </c>
       <c r="F53">
-        <v>3.198307342511119</v>
+        <v>4.094077344141615</v>
       </c>
       <c r="G53">
-        <v>-4.651599668612801</v>
+        <v>-4.712656639390948</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.348083252915494</v>
       </c>
       <c r="E54">
-        <v>-10.16923387781231</v>
+        <v>-6.112232884502537</v>
       </c>
       <c r="F54">
-        <v>3.018864738981884</v>
+        <v>2.518787621585851</v>
       </c>
       <c r="G54">
-        <v>-4.477534146105818</v>
+        <v>-6.049682237990362</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.286082688736739</v>
       </c>
       <c r="E55">
-        <v>-8.823851420977492</v>
+        <v>-6.351657833762076</v>
       </c>
       <c r="F55">
-        <v>3.575063747917584</v>
+        <v>3.2846447634353</v>
       </c>
       <c r="G55">
-        <v>-3.634522703053282</v>
+        <v>-5.062438138849314</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.209255354357548</v>
       </c>
       <c r="E56">
-        <v>-8.898054996067179</v>
+        <v>-6.493996828771171</v>
       </c>
       <c r="F56">
-        <v>3.004981301310965</v>
+        <v>3.555577233134129</v>
       </c>
       <c r="G56">
-        <v>-5.410815275480238</v>
+        <v>-6.2289780276631</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.119855191247895</v>
       </c>
       <c r="E57">
-        <v>-8.819264076807723</v>
+        <v>-6.851270785606324</v>
       </c>
       <c r="F57">
-        <v>3.261276519002326</v>
+        <v>3.055964001483663</v>
       </c>
       <c r="G57">
-        <v>-4.335746000079093</v>
+        <v>-4.592084871967593</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.016916918545109</v>
       </c>
       <c r="E58">
-        <v>-7.839990629597024</v>
+        <v>-3.42460167484621</v>
       </c>
       <c r="F58">
-        <v>3.20887399710123</v>
+        <v>2.88428320051866</v>
       </c>
       <c r="G58">
-        <v>-4.957005927701237</v>
+        <v>-5.273200843277127</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.898238303808391</v>
       </c>
       <c r="E59">
-        <v>-7.515865102498018</v>
+        <v>-3.906807172604973</v>
       </c>
       <c r="F59">
-        <v>3.041409586216476</v>
+        <v>3.348079482406881</v>
       </c>
       <c r="G59">
-        <v>-5.208829838723941</v>
+        <v>-5.276170348788424</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.760084554569851</v>
       </c>
       <c r="E60">
-        <v>-6.65699019372925</v>
+        <v>-3.714659491985512</v>
       </c>
       <c r="F60">
-        <v>3.15389028237301</v>
+        <v>3.817712441015227</v>
       </c>
       <c r="G60">
-        <v>-4.999816025387312</v>
+        <v>-5.418243961090822</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.600129504352568</v>
       </c>
       <c r="E61">
-        <v>-6.689536336422377</v>
+        <v>-3.688869832511829</v>
       </c>
       <c r="F61">
-        <v>3.566844686547008</v>
+        <v>2.840724329009851</v>
       </c>
       <c r="G61">
-        <v>-5.210526230270173</v>
+        <v>-6.051545971836127</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.427364775195026</v>
       </c>
       <c r="E62">
-        <v>-6.182492158731542</v>
+        <v>-4.058098960727231</v>
       </c>
       <c r="F62">
-        <v>3.094168306100777</v>
+        <v>3.086666610901024</v>
       </c>
       <c r="G62">
-        <v>-5.430758540118544</v>
+        <v>-5.903008353061624</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.245914316213826</v>
       </c>
       <c r="E63">
-        <v>-5.427744981295147</v>
+        <v>-4.701454734522952</v>
       </c>
       <c r="F63">
-        <v>2.860901702207241</v>
+        <v>2.623412081294234</v>
       </c>
       <c r="G63">
-        <v>-5.439181435861638</v>
+        <v>-5.840967015815643</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.059690262298576</v>
       </c>
       <c r="E64">
-        <v>-6.418593208069452</v>
+        <v>-3.412007988630879</v>
       </c>
       <c r="F64">
-        <v>2.75669805313948</v>
+        <v>2.860412965439589</v>
       </c>
       <c r="G64">
-        <v>-5.612318372667298</v>
+        <v>-7.047357340468885</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.869214040379318</v>
       </c>
       <c r="E65">
-        <v>-5.500820966356923</v>
+        <v>-1.989709400775781</v>
       </c>
       <c r="F65">
-        <v>2.865591918441892</v>
+        <v>3.026870081562539</v>
       </c>
       <c r="G65">
-        <v>-5.241753615851409</v>
+        <v>-6.718214724619425</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.677591587869832</v>
       </c>
       <c r="E66">
-        <v>-6.454748544546692</v>
+        <v>-2.632218349932066</v>
       </c>
       <c r="F66">
-        <v>2.656419208826183</v>
+        <v>3.25153657508021</v>
       </c>
       <c r="G66">
-        <v>-5.246974039352486</v>
+        <v>-5.128239756002419</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.494051857745489</v>
       </c>
       <c r="E67">
-        <v>-5.312925522830665</v>
+        <v>-2.297618462453319</v>
       </c>
       <c r="F67">
-        <v>2.845446023205808</v>
+        <v>2.787178660092891</v>
       </c>
       <c r="G67">
-        <v>-5.801090330203712</v>
+        <v>-6.014369731567618</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.32108305226988</v>
       </c>
       <c r="E68">
-        <v>-6.127294589052048</v>
+        <v>-3.615132690244933</v>
       </c>
       <c r="F68">
-        <v>2.428406111001203</v>
+        <v>2.86937590073788</v>
       </c>
       <c r="G68">
-        <v>-5.05874348337338</v>
+        <v>-6.640571178858286</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.159627486078984</v>
       </c>
       <c r="E69">
-        <v>-5.695029102649874</v>
+        <v>-2.453660619809624</v>
       </c>
       <c r="F69">
-        <v>2.617830541734171</v>
+        <v>1.99179353380325</v>
       </c>
       <c r="G69">
-        <v>-4.34475295325977</v>
+        <v>-5.375446988290983</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.005410718630399</v>
       </c>
       <c r="E70">
-        <v>-5.337737031918691</v>
+        <v>-2.450526915796316</v>
       </c>
       <c r="F70">
-        <v>2.201126946695102</v>
+        <v>2.551620791963212</v>
       </c>
       <c r="G70">
-        <v>-4.16635293707276</v>
+        <v>-5.179085565287574</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.860043898438243</v>
       </c>
       <c r="E71">
-        <v>-4.51541143686583</v>
+        <v>-2.161900096443438</v>
       </c>
       <c r="F71">
-        <v>2.27821647393443</v>
+        <v>2.595128304693048</v>
       </c>
       <c r="G71">
-        <v>-4.707039188081179</v>
+        <v>-5.462018737915373</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.72675538002855</v>
       </c>
       <c r="E72">
-        <v>-5.393446319161051</v>
+        <v>-3.823125501417232</v>
       </c>
       <c r="F72">
-        <v>1.989146071583903</v>
+        <v>2.386613318795162</v>
       </c>
       <c r="G72">
-        <v>-3.830162257313614</v>
+        <v>-4.607778954686417</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.604621028582724</v>
       </c>
       <c r="E73">
-        <v>-5.194764050548522</v>
+        <v>-4.247158222073462</v>
       </c>
       <c r="F73">
-        <v>1.712799392540377</v>
+        <v>1.853747762861518</v>
       </c>
       <c r="G73">
-        <v>-3.942215973568651</v>
+        <v>-4.72168656112254</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.492001275432719</v>
       </c>
       <c r="E74">
-        <v>-5.519600548066732</v>
+        <v>-2.065289631963799</v>
       </c>
       <c r="F74">
-        <v>1.6082064107933</v>
+        <v>1.556088847278766</v>
       </c>
       <c r="G74">
-        <v>-2.639771168984225</v>
+        <v>-5.120423886247822</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.384362917278098</v>
       </c>
       <c r="E75">
-        <v>-5.361185470330407</v>
+        <v>-1.056771299611564</v>
       </c>
       <c r="F75">
-        <v>1.666919435568923</v>
+        <v>2.920292331518354</v>
       </c>
       <c r="G75">
-        <v>-4.056612482017131</v>
+        <v>-3.543498335772726</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.285572824861524</v>
       </c>
       <c r="E76">
-        <v>-5.138606444379402</v>
+        <v>-2.716420795630689</v>
       </c>
       <c r="F76">
-        <v>1.803643132135787</v>
+        <v>1.797031103526642</v>
       </c>
       <c r="G76">
-        <v>-3.725330509710914</v>
+        <v>-3.955856011591262</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.200058897760849</v>
       </c>
       <c r="E77">
-        <v>-5.504421103193021</v>
+        <v>-5.078318869915287</v>
       </c>
       <c r="F77">
-        <v>1.633640603528856</v>
+        <v>2.26006031719987</v>
       </c>
       <c r="G77">
-        <v>-2.670742619283824</v>
+        <v>-2.904470593406189</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.130984835432979</v>
       </c>
       <c r="E78">
-        <v>-6.662311150688263</v>
+        <v>-3.486791208393547</v>
       </c>
       <c r="F78">
-        <v>1.334218922112947</v>
+        <v>1.636059436345031</v>
       </c>
       <c r="G78">
-        <v>-3.435946455497247</v>
+        <v>-1.874206398399262</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.080791792159522</v>
       </c>
       <c r="E79">
-        <v>-7.63443413744085</v>
+        <v>-5.47792953024815</v>
       </c>
       <c r="F79">
-        <v>1.025433375575792</v>
+        <v>1.196055523000017</v>
       </c>
       <c r="G79">
-        <v>-2.779055742961094</v>
+        <v>-3.584356106630932</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.050773277160189</v>
       </c>
       <c r="E80">
-        <v>-8.500101757221124</v>
+        <v>-7.512980464555132</v>
       </c>
       <c r="F80">
-        <v>0.8253412294295712</v>
+        <v>1.805029819168074</v>
       </c>
       <c r="G80">
-        <v>-1.335180445499922</v>
+        <v>-2.770124257876285</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.050948532893623</v>
       </c>
       <c r="E81">
-        <v>-8.526683899646148</v>
+        <v>-2.936744641525875</v>
       </c>
       <c r="F81">
-        <v>1.228964903178436</v>
+        <v>1.078238484034649</v>
       </c>
       <c r="G81">
-        <v>-2.380646539991757</v>
+        <v>-3.177166354768521</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.08835997801464</v>
       </c>
       <c r="E82">
-        <v>-10.21388916000195</v>
+        <v>-8.820061088233073</v>
       </c>
       <c r="F82">
-        <v>1.128672804986694</v>
+        <v>0.900909874117359</v>
       </c>
       <c r="G82">
-        <v>-1.257694398373635</v>
+        <v>-2.287190787535653</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.167851567787263</v>
       </c>
       <c r="E83">
-        <v>-10.46805429215645</v>
+        <v>-6.921054570064523</v>
       </c>
       <c r="F83">
-        <v>0.8787493893576666</v>
+        <v>1.283615614210731</v>
       </c>
       <c r="G83">
-        <v>-0.5824682197633042</v>
+        <v>-0.5870127116231351</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.289379568309434</v>
       </c>
       <c r="E84">
-        <v>-11.11066739621492</v>
+        <v>-7.165066863493833</v>
       </c>
       <c r="F84">
-        <v>0.738392473362124</v>
+        <v>1.332751055075186</v>
       </c>
       <c r="G84">
-        <v>-1.020386611529915</v>
+        <v>-2.51027119769762</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.452046943909024</v>
       </c>
       <c r="E85">
-        <v>-11.32375021217184</v>
+        <v>-9.207562609069425</v>
       </c>
       <c r="F85">
-        <v>0.8143653613424778</v>
+        <v>0.836287276290164</v>
       </c>
       <c r="G85">
-        <v>-1.016153835718231</v>
+        <v>-0.1794357756167097</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.66075457028241</v>
       </c>
       <c r="E86">
-        <v>-13.42966723622485</v>
+        <v>-9.960249330832331</v>
       </c>
       <c r="F86">
-        <v>0.5255997981961814</v>
+        <v>0.9393063599719217</v>
       </c>
       <c r="G86">
-        <v>-0.349078211461561</v>
+        <v>-0.4492571868929676</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.914592537503088</v>
       </c>
       <c r="E87">
-        <v>-13.60321647409481</v>
+        <v>-11.49498539982388</v>
       </c>
       <c r="F87">
-        <v>0.8950516598447609</v>
+        <v>1.05852002637841</v>
       </c>
       <c r="G87">
-        <v>-0.3583345374807545</v>
+        <v>-1.871315642205391</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.21027633890981</v>
       </c>
       <c r="E88">
-        <v>-15.55611636142864</v>
+        <v>-14.42914673445778</v>
       </c>
       <c r="F88">
-        <v>0.3284011393879395</v>
+        <v>0.8248508359271139</v>
       </c>
       <c r="G88">
-        <v>0.2386246632721415</v>
+        <v>0.1578180199276965</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.53706908111362</v>
       </c>
       <c r="E89">
-        <v>-16.19421004842745</v>
+        <v>-13.60503692064589</v>
       </c>
       <c r="F89">
-        <v>0.5748205609031252</v>
+        <v>0.417579860503723</v>
       </c>
       <c r="G89">
-        <v>0.3204255167490982</v>
+        <v>-1.114915323435958</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.888353912611371</v>
       </c>
       <c r="E90">
-        <v>-19.15418368490507</v>
+        <v>-17.8754196091971</v>
       </c>
       <c r="F90">
-        <v>0.04100818102808177</v>
+        <v>-0.04112776042910041</v>
       </c>
       <c r="G90">
-        <v>0.1219378621751685</v>
+        <v>1.020648041199279</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.261754174376732</v>
       </c>
       <c r="E91">
-        <v>-20.1357168406456</v>
+        <v>-18.04325391286937</v>
       </c>
       <c r="F91">
-        <v>-0.290902898293027</v>
+        <v>0.6241208468807378</v>
       </c>
       <c r="G91">
-        <v>-0.1194025459651092</v>
+        <v>0.5049843858031852</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.650087778373431</v>
       </c>
       <c r="E92">
-        <v>-22.49560427247079</v>
+        <v>-19.50088365493232</v>
       </c>
       <c r="F92">
-        <v>-0.3127022148650987</v>
+        <v>0.05796320502858206</v>
       </c>
       <c r="G92">
-        <v>0.04803162777023574</v>
+        <v>1.447170750489938</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.045528075043359</v>
       </c>
       <c r="E93">
-        <v>-21.91416179530794</v>
+        <v>-21.34075735950871</v>
       </c>
       <c r="F93">
-        <v>-0.2748764741510649</v>
+        <v>-0.7344439404479942</v>
       </c>
       <c r="G93">
-        <v>0.3506291612037869</v>
+        <v>-0.8601317505666349</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.432513666182176</v>
       </c>
       <c r="E94">
-        <v>-25.6443156486401</v>
+        <v>-24.43226958048713</v>
       </c>
       <c r="F94">
-        <v>-0.2459101228099718</v>
+        <v>0.5069457926525393</v>
       </c>
       <c r="G94">
-        <v>-0.3851257115136206</v>
+        <v>-1.633768326187832</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.807311906536444</v>
       </c>
       <c r="E95">
-        <v>-26.28867674366552</v>
+        <v>-25.34235247333463</v>
       </c>
       <c r="F95">
-        <v>-0.8310696845149453</v>
+        <v>-0.9718432693140961</v>
       </c>
       <c r="G95">
-        <v>-0.2847006444652557</v>
+        <v>-0.2297434645661161</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.165221233648763</v>
       </c>
       <c r="E96">
-        <v>-29.26813640379815</v>
+        <v>-27.7678167372649</v>
       </c>
       <c r="F96">
-        <v>-0.8068283408394207</v>
+        <v>-0.8550542342956022</v>
       </c>
       <c r="G96">
-        <v>0.5489625983644227</v>
+        <v>-0.6127309262060627</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.498932161282006</v>
       </c>
       <c r="E97">
-        <v>-31.59024730545136</v>
+        <v>-29.91977022807989</v>
       </c>
       <c r="F97">
-        <v>-1.265430759112089</v>
+        <v>-0.5708604308453562</v>
       </c>
       <c r="G97">
-        <v>-0.5183072133899221</v>
+        <v>-0.956809662594114</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.79819557382501</v>
       </c>
       <c r="E98">
-        <v>-32.82741508316188</v>
+        <v>-31.96915604685815</v>
       </c>
       <c r="F98">
-        <v>-1.476603976005558</v>
+        <v>-0.9307976645053806</v>
       </c>
       <c r="G98">
-        <v>-1.316169047784499</v>
+        <v>-1.90459051003972</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.04788777623877</v>
       </c>
       <c r="E99">
-        <v>-36.17558083276202</v>
+        <v>-33.60483859419168</v>
       </c>
       <c r="F99">
-        <v>-1.781193013280131</v>
+        <v>-0.8372120288067036</v>
       </c>
       <c r="G99">
-        <v>-0.9767299586815029</v>
+        <v>-0.4284673670923259</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.24213257578724</v>
       </c>
       <c r="E100">
-        <v>-38.23318809610121</v>
+        <v>-37.15479767404763</v>
       </c>
       <c r="F100">
-        <v>-1.710998816301706</v>
+        <v>-1.442722920863656</v>
       </c>
       <c r="G100">
-        <v>-1.002290674629577</v>
+        <v>-2.538886730917538</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.3767496192902</v>
       </c>
       <c r="E101">
-        <v>-40.57218567732902</v>
+        <v>-40.78254461617033</v>
       </c>
       <c r="F101">
-        <v>-1.777183715050581</v>
+        <v>-1.107920839306777</v>
       </c>
       <c r="G101">
-        <v>-2.001015768007122</v>
+        <v>-3.04327282781382</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.4394568391362</v>
       </c>
       <c r="E102">
-        <v>-43.34688585673082</v>
+        <v>-42.21281784675293</v>
       </c>
       <c r="F102">
-        <v>-1.599675349406883</v>
+        <v>-1.5023595752934</v>
       </c>
       <c r="G102">
-        <v>-2.674335556891415</v>
+        <v>-2.823506451426891</v>
       </c>
     </row>
   </sheetData>
